--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484585_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484585_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1558</v>
+        <v>1.7633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7262</v>
+        <v>0.2594</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4296</v>
+        <v>1.5039</v>
       </c>
       <c r="G2" t="n">
         <v>1.7307</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1582</v>
+        <v>-0.2343</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0589</v>
+        <v>0.592</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8264</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0463</v>
+        <v>1.5753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5737</v>
+        <v>1.5753</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4726</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5617</v>
+        <v>1.5753</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0489</v>
+        <v>0.3251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5128</v>
+        <v>1.2502</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8486</v>
+        <v>1.5753</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4335</v>
+        <v>0.3251</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2821</v>
+        <v>1.2502</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2869</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4824</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7692</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7075</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6659</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0416</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5753</v>
+        <v>1.0348</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5753</v>
+        <v>-0.1405</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.1753</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5753</v>
+        <v>-0.5617</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3251</v>
+        <v>-0.0489</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2502</v>
+        <v>-0.5128</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5753</v>
+        <v>-0.8486</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3251</v>
+        <v>0.4335</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2502</v>
+        <v>-1.2821</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.2869</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.4824</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.7692</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.9517</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.2557</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1751</v>
+        <v>0.84</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5526</v>
+        <v>0.168</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="G5" t="n">
         <v>0.3178</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3075</v>
+        <v>-0.0275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5309</v>
+        <v>0.1463</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2234</v>
+        <v>-0.1738</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8874</v>
+        <v>0.3895</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5198</v>
+        <v>-1.2878</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6324</v>
+        <v>1.6773</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6819</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3006</v>
+        <v>-0.1194</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3813</v>
+        <v>0.6925</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9341</v>
+        <v>-0.1777</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2256</v>
+        <v>0.4118</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7085</v>
+        <v>-0.5895</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2522</v>
+        <v>0.7508</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.925</v>
+        <v>-0.5312</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6729000000000001</v>
+        <v>1.2821</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6191</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4812</v>
+        <v>-0.1938</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8621</v>
+        <v>-0.5396</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5131</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3781</v>
+        <v>-0.1312</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1505</v>
+        <v>1.2287</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5286</v>
+        <v>-1.3599</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5731000000000001</v>
+        <v>1.6819</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1194</v>
+        <v>0.3006</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6925</v>
+        <v>1.3813</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1777</v>
+        <v>1.9341</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4118</v>
+        <v>1.2256</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5895</v>
+        <v>0.7085</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7508</v>
+        <v>-0.2522</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5312</v>
+        <v>-0.925</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2821</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7448</v>
+        <v>-0.3995</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0565</v>
+        <v>0.1901</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6882</v>
+        <v>-0.5896</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.5131</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5261</v>
+        <v>-1.9036</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2213</v>
+        <v>-1.5378</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3048</v>
+        <v>-0.3658</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.222</v>
+        <v>-0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6961</v>
+        <v>0.9449</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5259</v>
+        <v>-0.9649</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.471</v>
+        <v>-0.5692</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0867</v>
+        <v>1.8699</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5577</v>
+        <v>-2.4391</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.751</v>
+        <v>0.5492</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7828</v>
+        <v>-0.925</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0318</v>
+        <v>1.4742</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3725</v>
+        <v>-0.5775</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.101</v>
+        <v>-0.0524</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2714</v>
+        <v>-0.5251</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0312</v>
+        <v>-2.2224</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2982</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9596</v>
+        <v>-2.0115</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.337</v>
+        <v>-3.5127</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3774</v>
+        <v>1.5012</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0966</v>
@@ -1156,13 +1156,13 @@
         <v>2.7489</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6406</v>
+        <v>-0.6925</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0279</v>
+        <v>-0.2036</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6128</v>
+        <v>-0.4889</v>
       </c>
       <c r="V9" t="n">
         <v>0.945</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GARRIDO TALENS</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1039</v>
+        <v>-2.1256</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6412</v>
+        <v>-0.5483</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5374</v>
+        <v>-1.5773</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5128</v>
+        <v>-2.222</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9069</v>
+        <v>-1.6961</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3942</v>
+        <v>-0.5259</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1662</v>
+        <v>-0.471</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2078</v>
+        <v>0.0867</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>-0.5577</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3466</v>
+        <v>-1.751</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.7828</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3525</v>
+        <v>0.0318</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0582</v>
+        <v>-0.9719</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2738</v>
+        <v>-0.428</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2155</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.0312</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>M. GARRIDO TALENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2011</v>
+        <v>-3.3457</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5133</v>
+        <v>-3.8336</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6878</v>
+        <v>0.4878</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.02</v>
+        <v>-1.5128</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9449</v>
+        <v>-1.9069</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9649</v>
+        <v>0.3942</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5692</v>
+        <v>-1.1662</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8699</v>
+        <v>-1.2078</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4391</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5492</v>
+        <v>-0.3466</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.925</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4742</v>
+        <v>0.3525</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.875</v>
+        <v>-0.1836</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0279</v>
+        <v>0.0815</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8471</v>
+        <v>-0.2651</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2592</v>
+        <v>-3.7016</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5611</v>
+        <v>-2.9291</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.7725</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5476</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5443</v>
+        <v>0.0134</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5694</v>
+        <v>0.0626</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0251</v>
+        <v>-0.0492</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4786</v>
+        <v>-8.1439</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.542199999999999</v>
+        <v>-7.9102</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0636</v>
+        <v>-0.2337</v>
       </c>
       <c r="G13" t="n">
         <v>-3.137</v>
@@ -1468,13 +1468,13 @@
         <v>2.5656</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8023</v>
+        <v>-0.4676</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7903</v>
+        <v>-0.1583</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0119</v>
+        <v>-0.3092</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5235</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.3105</v>
+        <v>-15.7602</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.019</v>
+        <v>-18.4686</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7086</v>
+        <v>2.7083</v>
       </c>
       <c r="G14" t="n">
         <v>-9.2189</v>
@@ -1516,13 +1516,13 @@
         <v>-8.5777</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6410999999999998</v>
+        <v>-0.6411000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.101899999999999</v>
+        <v>-8.101900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8709999999999991</v>
+        <v>0.8710000000000009</v>
       </c>
       <c r="L14" t="n">
         <v>-8.973000000000001</v>
@@ -1531,7 +1531,7 @@
         <v>-1.1169</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.448699999999999</v>
+        <v>-9.448700000000001</v>
       </c>
       <c r="O14" t="n">
         <v>8.332000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>20.1583</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.129</v>
+        <v>-3.5783</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4377000000000002</v>
+        <v>0.9880999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.5664</v>
+        <v>-4.5665</v>
       </c>
       <c r="V14" t="n">
         <v>-5.7117</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.7174</v>
+        <v>11.6304</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6622</v>
+        <v>6.893</v>
       </c>
       <c r="F15" t="n">
-        <v>5.0552</v>
+        <v>4.7374</v>
       </c>
       <c r="G15" t="n">
         <v>7.0655</v>
@@ -1624,13 +1624,13 @@
         <v>2.3823</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5632</v>
+        <v>1.4762</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7383</v>
+        <v>0.9691</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8248</v>
+        <v>0.5071</v>
       </c>
       <c r="V15" t="n">
         <v>3.8217</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3475</v>
+        <v>4.8676</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9588</v>
+        <v>1.2473</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3887</v>
+        <v>3.6204</v>
       </c>
       <c r="G16" t="n">
         <v>3.9439</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3145</v>
+        <v>0.8346</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3643</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0497</v>
+        <v>0.1819</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6439</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3306</v>
+        <v>2.6147</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1833</v>
+        <v>-1.2794</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5138</v>
+        <v>3.8941</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1978</v>
@@ -1780,13 +1780,13 @@
         <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>1.201</v>
+        <v>1.4851</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4457</v>
+        <v>1.3496</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2448</v>
+        <v>0.1355</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3219</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1127</v>
+        <v>2.0379</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0187</v>
+        <v>0.6544</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1314</v>
+        <v>1.3835</v>
       </c>
       <c r="G18" t="n">
         <v>0.4383</v>
@@ -1858,13 +1858,13 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8699</v>
+        <v>0.0552</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5324</v>
+        <v>0.1407</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3375</v>
+        <v>-0.0854</v>
       </c>
       <c r="V18" t="n">
         <v>1.9109</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0572</v>
+        <v>1.5191</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3168</v>
+        <v>-0.0283</v>
       </c>
       <c r="F19" t="n">
-        <v>1.374</v>
+        <v>1.5474</v>
       </c>
       <c r="G19" t="n">
         <v>0.3736</v>
@@ -1936,13 +1936,13 @@
         <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4892</v>
+        <v>-0.0273</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2202</v>
+        <v>0.0683</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.269</v>
+        <v>-0.0956</v>
       </c>
       <c r="V19" t="n">
         <v>0.6231</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3551</v>
+        <v>-0.608</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3647</v>
+        <v>-3.1339</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7198</v>
+        <v>2.5259</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5674</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8388</v>
+        <v>0.8757</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3726</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4663</v>
+        <v>0.2724</v>
       </c>
       <c r="V20" t="n">
         <v>1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4825</v>
+        <v>-0.9211</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9212</v>
+        <v>-2.0173</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4387</v>
+        <v>1.0962</v>
       </c>
       <c r="G21" t="n">
         <v>1.0124</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>1.466</v>
+        <v>1.0273</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6765</v>
+        <v>0.5803</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7895</v>
+        <v>0.447</v>
       </c>
       <c r="V21" t="n">
         <v>-0.945</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4865</v>
+        <v>-0.9843</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3683</v>
+        <v>-4.7914</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8819</v>
+        <v>3.8072</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6904</v>
@@ -2170,13 +2170,13 @@
         <v>2.7489</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6257</v>
+        <v>-0.1235</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3869</v>
+        <v>0.1901</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2389</v>
+        <v>-0.3136</v>
       </c>
       <c r="V22" t="n">
         <v>2.8455</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6411</v>
+        <v>-2.5638</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1566</v>
+        <v>-0.2528</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4844</v>
+        <v>-2.311</v>
       </c>
       <c r="G23" t="n">
         <v>0.8407</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2698</v>
+        <v>-0.1925</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1086</v>
+        <v>0.0125</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3784</v>
+        <v>-0.205</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8455</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.3104</v>
+        <v>17.5925</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7086</v>
+        <v>-2.708400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>19.0191</v>
+        <v>20.3011</v>
       </c>
       <c r="G24" t="n">
         <v>9.2188</v>
@@ -2326,13 +2326,13 @@
         <v>17.4095</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1289</v>
+        <v>5.4108</v>
       </c>
       <c r="T24" t="n">
-        <v>4.5665</v>
+        <v>4.5666</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4377</v>
+        <v>0.8443000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>5.7119</v>
